--- a/exibir_NF/invoice-processor/spreadsheets/Card_Clayton_Pires_Dos_Santos_5885_MAIO_2026.xlsx
+++ b/exibir_NF/invoice-processor/spreadsheets/Card_Clayton_Pires_Dos_Santos_5885_MAIO_2026.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="DD/MM/YYYY"/>
     <numFmt numFmtId="165" formatCode="R$ #,##0.00;(R$ #,##0.00)"/>
-    <numFmt numFmtId="166" formatCode="R$ #,##0.00; R$( -#,##0.00)"/>
+    <numFmt numFmtId="166" formatCode="R$ #,##0.00"/>
   </numFmts>
   <fonts count="5">
     <font>
